--- a/results/Int Task Remove ACC 0.6/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC 0.6/Rando_3_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4256257561342307</v>
+        <v>0.4456177983720356</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4256257561342307</v>
+        <v>0.4470302277505667</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4242133267556997</v>
+        <v>0.4615076288805102</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4242133267556997</v>
+        <v>0.4615076288805102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4252726487895979</v>
+        <v>0.4621940225753786</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4178970365411043</v>
+        <v>0.4400473648355004</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4186230722247671</v>
+        <v>0.4400473648355004</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4196427522698709</v>
+        <v>0.4367504727674219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4207218952981665</v>
+        <v>0.4342787213549926</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4246060760891269</v>
+        <v>0.4342787213549926</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.415131640767234</v>
+        <v>0.4347903966548035</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4204084299423283</v>
+        <v>0.4325924686094177</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4179564995242961</v>
+        <v>0.4470896907337585</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4194085708916218</v>
+        <v>0.4425587582367244</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4205075349143146</v>
+        <v>0.4432649729259899</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4186627142135617</v>
+        <v>0.4396149735132786</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3964800850394071</v>
+        <v>0.4407337585303687</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4077398780788611</v>
+        <v>0.4474427980783913</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4115249538978353</v>
+        <v>0.4477760844286268</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4122509895814981</v>
+        <v>0.4548778733100767</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4122509895814981</v>
+        <v>0.455564267004945</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4008722705756604</v>
+        <v>0.4464429390276848</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.39736101812373</v>
+        <v>0.4453836169937865</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3980672328129956</v>
+        <v>0.424689030621234</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4155677026439739</v>
+        <v>0.4297316384180791</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4169603110281076</v>
+        <v>0.4322033898305085</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4246493886324395</v>
+        <v>0.4318502824858757</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4354569693552744</v>
+        <v>0.4449152542372881</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4280813571067809</v>
+        <v>0.4540365822145483</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4432055099427981</v>
+        <v>0.4518981171523545</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4432055099427981</v>
+        <v>0.4628048028471757</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4534654439315456</v>
+        <v>0.4628048028471757</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4534654439315456</v>
+        <v>0.4606861587793791</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4559768373327696</v>
+        <v>0.4617653018076747</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4559768373327696</v>
+        <v>0.4607258007681737</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.458234228361347</v>
+        <v>0.4560759423047559</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4610590871184091</v>
+        <v>0.4514459048357353</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4571749063274487</v>
+        <v>0.4532312625532964</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4571749063274487</v>
+        <v>0.4549373362932685</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.461491478440631</v>
+        <v>0.4480932203389831</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4625508004745292</v>
+        <v>0.4442090395480226</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4625706214689266</v>
+        <v>0.442090395480226</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.463570480519633</v>
+        <v>0.4417372881355932</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.463570480519633</v>
+        <v>0.5384541973525024</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.463570480519633</v>
+        <v>0.537239977917944</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.467121374960358</v>
+        <v>0.5421041967652137</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.475635593220339</v>
+        <v>0.5421041967652137</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4781073446327684</v>
+        <v>0.5355537251723692</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4855225988700565</v>
+        <v>0.6402893277893278</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4798728813559322</v>
+        <v>0.54930509061865</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4830508474576271</v>
+        <v>0.5423816906867754</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4706920903954802</v>
+        <v>0.5225915289474612</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4713983050847458</v>
+        <v>0.5225915289474612</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4713983050847458</v>
+        <v>0.5040192571972233</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4624913374913375</v>
+        <v>0.5226906339194475</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4427929396149735</v>
+        <v>0.5251190727885643</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4427731186205762</v>
+        <v>0.5343952981664846</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4418327225530615</v>
+        <v>0.535533904177972</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4879003840868248</v>
+        <v>0.5465756662790561</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.444086443027121</v>
+        <v>0.549007775702691</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4392978376029223</v>
+        <v>0.5913857958349484</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.441416481670719</v>
+        <v>0.6017051928068877</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4397302289251442</v>
+        <v>0.4911290038408683</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.416464786168176</v>
+        <v>0.4682129978740148</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4212262294889414</v>
+        <v>0.4682129978740148</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4090656823707671</v>
+        <v>0.4428722235925626</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4135767938734041</v>
+        <v>0.4517197282027791</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4006109270939779</v>
+        <v>0.4602339464627601</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4493536887604684</v>
+        <v>0.4602339464627601</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4536107978904589</v>
+        <v>0.4602339464627601</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4536504398792535</v>
+        <v>0.4602339464627601</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4473106581157429</v>
+        <v>0.4668996734674701</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4421887663413087</v>
+        <v>0.4435982592762254</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.446426054476902</v>
+        <v>0.4353380433888909</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.455388814498984</v>
+        <v>0.4350245780330526</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.455388814498984</v>
+        <v>0.3896521195250009</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4477195578890494</v>
+        <v>0.3840024020108765</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4264648448970483</v>
+        <v>0.3967142664176563</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4456530356954086</v>
+        <v>0.393730839705416</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4595791195367467</v>
+        <v>0.4026378072988243</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4362417339112254</v>
+        <v>0.3939452000892679</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4927132151708423</v>
+        <v>0.4130328176938346</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4793186276237124</v>
+        <v>0.4418129015586643</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5161783360935903</v>
+        <v>0.4262959993892197</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5168449087940613</v>
+        <v>0.452006031455184</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5168449087940613</v>
+        <v>0.4660906832517002</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5137065846811609</v>
+        <v>0.4954918249409775</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5121194369075726</v>
+        <v>0.4809300010571197</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5121392579019698</v>
+        <v>0.5293159848244594</v>
       </c>
     </row>
   </sheetData>
